--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484196_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484196_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.507</v>
+        <v>6.3817</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9395</v>
+        <v>3.7581</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5675</v>
+        <v>2.6236</v>
       </c>
       <c r="G2" t="n">
         <v>3.4267</v>
@@ -610,13 +610,13 @@
         <v>2.7774</v>
       </c>
       <c r="S2" t="n">
-        <v>0.08840000000000001</v>
+        <v>-0.0369</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1303</v>
+        <v>-0.3117</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2187</v>
+        <v>0.2748</v>
       </c>
       <c r="V2" t="n">
         <v>1.2065</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3959</v>
+        <v>4.8587</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0494</v>
+        <v>3.3158</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3465</v>
+        <v>1.5429</v>
       </c>
       <c r="G3" t="n">
         <v>1.0532</v>
@@ -688,13 +688,13 @@
         <v>2.7774</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1217</v>
+        <v>-0.6589</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1222</v>
+        <v>-0.8558</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0005</v>
+        <v>0.1969</v>
       </c>
       <c r="V3" t="n">
         <v>2.6789</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. TROUVE CASELLAS</t>
+          <t>G. FABREGAS CANALS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9942</v>
+        <v>4.0926</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1047</v>
+        <v>3.1412</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8895</v>
+        <v>0.9514</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6417</v>
+        <v>3.1143</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3941</v>
+        <v>1.0284</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2476</v>
+        <v>2.0859</v>
       </c>
       <c r="J4" t="n">
-        <v>5.0861</v>
+        <v>3.7554</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1908</v>
+        <v>1.8251</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8953</v>
+        <v>1.9303</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4444</v>
+        <v>-0.6412</v>
       </c>
       <c r="N4" t="n">
         <v>-0.7967</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6477000000000001</v>
+        <v>0.1555</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5952</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R4" t="n">
-        <v>2.579</v>
+        <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2427</v>
+        <v>0.2876</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.3174</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7549</v>
+        <v>0.605</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.881</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.6789</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.7979000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. FABREGAS CANALS</t>
+          <t>A. TROUVE CASELLAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7397</v>
+        <v>3.7564</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6481</v>
+        <v>2.2691</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0916</v>
+        <v>1.4873</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1143</v>
+        <v>3.6417</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0284</v>
+        <v>2.3941</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0859</v>
+        <v>1.2476</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7554</v>
+        <v>5.0861</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8251</v>
+        <v>3.1908</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9303</v>
+        <v>1.8953</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6412</v>
+        <v>-1.4444</v>
       </c>
       <c r="N5" t="n">
         <v>-0.7967</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1555</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7855</v>
+        <v>2.579</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.4804</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8105</v>
+        <v>-0.8331</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7453</v>
+        <v>0.3527</v>
       </c>
       <c r="V5" t="n">
-        <v>1.881</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6789</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7979000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6723</v>
+        <v>3.6935</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3616</v>
+        <v>3.2425</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3107</v>
+        <v>0.4509</v>
       </c>
       <c r="G6" t="n">
         <v>-1.1857</v>
@@ -922,13 +922,13 @@
         <v>1.9838</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0708</v>
+        <v>-0.0496</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3797</v>
+        <v>-0.4987</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3089</v>
+        <v>0.4491</v>
       </c>
       <c r="V6" t="n">
         <v>2.9449</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.2212</v>
+        <v>3.2811</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0103</v>
+        <v>0.3787</v>
       </c>
       <c r="F7" t="n">
-        <v>3.211</v>
+        <v>2.9024</v>
       </c>
       <c r="G7" t="n">
         <v>-1.7208</v>
@@ -1000,13 +1000,13 @@
         <v>2.9758</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7839</v>
+        <v>-0.7241</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2469</v>
+        <v>-0.8784999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.463</v>
+        <v>0.1544</v>
       </c>
       <c r="V7" t="n">
         <v>2.7502</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. BESORA TOMAS</t>
+          <t>J. CAÑELLAS VAQUÉ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.6128</v>
+        <v>2.7407</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4977</v>
+        <v>1.3973</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8849</v>
+        <v>1.3434</v>
       </c>
       <c r="G8" t="n">
-        <v>5.223</v>
+        <v>0.5642</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8729</v>
+        <v>-0.2676</v>
       </c>
       <c r="I8" t="n">
-        <v>2.35</v>
+        <v>0.8318</v>
       </c>
       <c r="J8" t="n">
-        <v>7.1985</v>
+        <v>1.6069</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5336</v>
+        <v>0.121</v>
       </c>
       <c r="L8" t="n">
-        <v>3.6649</v>
+        <v>1.486</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9755</v>
+        <v>-1.0428</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6607</v>
+        <v>-0.3886</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3149</v>
+        <v>-0.6542</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7935</v>
+        <v>2.3806</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7774</v>
+        <v>2.3806</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6535</v>
+        <v>-0.2041</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3797</v>
+        <v>-0.2097</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2738</v>
+        <v>0.0056</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.7502</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CAÑELLAS VAQUÉ</t>
+          <t>O. BESORA TOMAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.5957</v>
+        <v>2.5592</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4767</v>
+        <v>4.1916</v>
       </c>
       <c r="F9" t="n">
-        <v>1.119</v>
+        <v>-1.6324</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5642</v>
+        <v>5.223</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2676</v>
+        <v>2.8729</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8318</v>
+        <v>2.35</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6069</v>
+        <v>7.1985</v>
       </c>
       <c r="K9" t="n">
-        <v>0.121</v>
+        <v>3.5336</v>
       </c>
       <c r="L9" t="n">
-        <v>1.486</v>
+        <v>3.6649</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0428</v>
+        <v>-1.9755</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3886</v>
+        <v>-0.6607</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6542</v>
+        <v>-1.3149</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3806</v>
+        <v>0.7935</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3806</v>
+        <v>2.7774</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3491</v>
+        <v>-0.7071</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1303</v>
+        <v>-0.6858</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2188</v>
+        <v>-0.0213</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.7502</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8158</v>
+        <v>-2.459</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6334</v>
+        <v>-0.3046</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1824</v>
+        <v>-2.1543</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6997</v>
@@ -1234,13 +1234,13 @@
         <v>1.7855</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8258</v>
+        <v>-0.469</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1222</v>
+        <v>-0.7935</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2964</v>
+        <v>0.3244</v>
       </c>
       <c r="V10" t="n">
         <v>-2.0757</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>27.923</v>
+        <v>28.9049</v>
       </c>
       <c r="E11" t="n">
-        <v>20.4546</v>
+        <v>21.3897</v>
       </c>
       <c r="F11" t="n">
-        <v>7.468500000000001</v>
+        <v>7.515199999999999</v>
       </c>
       <c r="G11" t="n">
         <v>12.4169</v>
@@ -1312,13 +1312,13 @@
         <v>21.8224</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.0243</v>
+        <v>-3.0425</v>
       </c>
       <c r="T11" t="n">
-        <v>-6.3193</v>
+        <v>-5.3842</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2951</v>
+        <v>2.3416</v>
       </c>
       <c r="V11" t="n">
         <v>6.6356</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.7276</v>
+        <v>1.4677</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3894</v>
+        <v>2.0833</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3383</v>
+        <v>-0.6156</v>
       </c>
       <c r="G12" t="n">
         <v>2.0442</v>
@@ -1390,13 +1390,13 @@
         <v>1.5871</v>
       </c>
       <c r="S12" t="n">
-        <v>2.3397</v>
+        <v>1.0797</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.306</v>
+        <v>-0.6121</v>
       </c>
       <c r="U12" t="n">
-        <v>2.6457</v>
+        <v>1.6918</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0611</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4172</v>
+        <v>0.2693</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4396</v>
+        <v>3.2355</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.0224</v>
+        <v>-2.9663</v>
       </c>
       <c r="G13" t="n">
         <v>2.5041</v>
@@ -1468,13 +1468,13 @@
         <v>0.7935</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4569</v>
+        <v>0.3089</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0566</v>
+        <v>-0.2607</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5135</v>
+        <v>0.5696</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1469</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.2555</v>
+        <v>-0.6306</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.329</v>
+        <v>-0.1249</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9265</v>
+        <v>-0.5057</v>
       </c>
       <c r="G14" t="n">
         <v>-0.5823</v>
@@ -1546,13 +1546,13 @@
         <v>1.1903</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5526</v>
+        <v>0.0723</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0599</v>
+        <v>-0.8558</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5072</v>
+        <v>0.9281</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1206</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. VICENTE ALONSO</t>
+          <t>J. ROYO SANTOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.3224</v>
+        <v>-1.2892</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0388</v>
+        <v>-0.651</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.3612</v>
+        <v>-0.6382</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.1853</v>
+        <v>-1.676</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.3184</v>
+        <v>-1.1138</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.8669</v>
+        <v>-0.5623</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5457</v>
+        <v>-0.617</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.312</v>
+        <v>-0.5794</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8576</v>
+        <v>-0.0376</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.731</v>
+        <v>-1.059</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.0064</v>
+        <v>-0.5344</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.7246</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.9838</v>
+        <v>0.3968</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.3725</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3887</v>
+        <v>0.3968</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6241</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.357</v>
+        <v>-0.034</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9811</v>
+        <v>0.0241</v>
       </c>
       <c r="V15" t="n">
-        <v>4.2226</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>4.2226</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. ROYO SANTOS</t>
+          <t>A. VICENTE ALONSO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.6335</v>
+        <v>-1.4066</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.855</v>
+        <v>2.0388</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7785</v>
+        <v>-3.4454</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.676</v>
+        <v>-4.1853</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1138</v>
+        <v>-2.3184</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5623</v>
+        <v>-1.8669</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.617</v>
+        <v>1.5457</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5794</v>
+        <v>-0.312</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0376</v>
+        <v>1.8576</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.059</v>
+        <v>-5.731</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5344</v>
+        <v>-2.0064</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-3.7246</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3968</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.3725</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3968</v>
+        <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3542</v>
+        <v>0.5399</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.238</v>
+        <v>-0.357</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1162</v>
+        <v>0.8969</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4.2226</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>4.2226</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.907</v>
+        <v>-3.4171</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0127</v>
+        <v>-1.5229</v>
       </c>
       <c r="F17" t="n">
         <v>-1.8943</v>
@@ -1780,10 +1780,10 @@
         <v>0.5952</v>
       </c>
       <c r="S17" t="n">
-        <v>1.111</v>
+        <v>0.6009</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9467</v>
+        <v>0.4365</v>
       </c>
       <c r="U17" t="n">
         <v>0.1643</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. PARDOS MARTINEZ</t>
+          <t>S. RODRIGUEZ ALEJANDRE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.7088</v>
+        <v>-3.8995</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3337</v>
+        <v>-2.3091</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.3751</v>
+        <v>-1.5904</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.9119</v>
+        <v>-1.7644</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5645</v>
+        <v>-0.8718</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3474</v>
+        <v>-0.8925999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6399</v>
+        <v>-0.5742</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0403</v>
+        <v>0.0658</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6802</v>
+        <v>-0.64</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.272</v>
+        <v>-1.1902</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6048</v>
+        <v>-0.9376</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6672</v>
+        <v>-0.2526</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1984</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1984</v>
+        <v>-1.9838</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.5952</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4059</v>
+        <v>0.1941</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5044999999999999</v>
+        <v>-0.017</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.09859999999999999</v>
+        <v>0.2111</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.0044</v>
+        <v>-0.9405</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.0044</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ ALEJANDRE</t>
+          <t>G. PARDOS MARTINEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.3356</v>
+        <v>-4.0608</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7172</v>
+        <v>-0.7419</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6185</v>
+        <v>-3.319</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7644</v>
+        <v>-1.9119</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8718</v>
+        <v>-0.5645</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8925999999999999</v>
+        <v>-1.3474</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5742</v>
+        <v>-0.6399</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0658</v>
+        <v>0.0403</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.64</v>
+        <v>-0.6802</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1902</v>
+        <v>-1.272</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9376</v>
+        <v>-0.6048</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2526</v>
+        <v>-0.6672</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3887</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9838</v>
+        <v>-0.1984</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5952</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.242</v>
+        <v>0.0539</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4251</v>
+        <v>0.0964</v>
       </c>
       <c r="U19" t="n">
-        <v>0.183</v>
+        <v>-0.0425</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9405</v>
+        <v>-2.0044</v>
       </c>
       <c r="W19" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2065</v>
+        <v>-2.0044</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.5558</v>
+        <v>-6.696</v>
       </c>
       <c r="E20" t="n">
         <v>-5.909</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6468</v>
+        <v>-0.7871</v>
       </c>
       <c r="G20" t="n">
         <v>-3.7266</v>
@@ -2014,13 +2014,13 @@
         <v>1.3887</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9381</v>
+        <v>0.7978</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3173</v>
       </c>
       <c r="U20" t="n">
-        <v>1.2554</v>
+        <v>1.1151</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9899</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-9.3492</v>
+        <v>-8.2601</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.1796</v>
+        <v>-3.5674</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.1696</v>
+        <v>-4.6927</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4117</v>
@@ -2092,13 +2092,13 @@
         <v>0.9919</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7023</v>
+        <v>0.3869</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9862</v>
+        <v>-0.374</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2839</v>
+        <v>0.7609</v>
       </c>
       <c r="V21" t="n">
         <v>-2.8708</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-27.923</v>
+        <v>-27.9229</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.468399999999998</v>
+        <v>-7.4686</v>
       </c>
       <c r="F22" t="n">
-        <v>-20.4546</v>
+        <v>-20.4547</v>
       </c>
       <c r="G22" t="n">
         <v>-12.4169</v>
@@ -2155,7 +2155,7 @@
         <v>-24.5248</v>
       </c>
       <c r="N22" t="n">
-        <v>-9.302800000000001</v>
+        <v>-9.302799999999998</v>
       </c>
       <c r="O22" t="n">
         <v>-15.2221</v>
@@ -2167,16 +2167,16 @@
         <v>-21.8222</v>
       </c>
       <c r="R22" t="n">
-        <v>8.9274</v>
+        <v>8.927399999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>4.0246</v>
+        <v>4.024500000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.2949</v>
+        <v>-2.295</v>
       </c>
       <c r="U22" t="n">
-        <v>6.3193</v>
+        <v>6.319400000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-6.6355</v>
